--- a/py project/rocket/generated_data/initial_sets/rocket_initial_n70.xlsx
+++ b/py project/rocket/generated_data/initial_sets/rocket_initial_n70.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>头锥外形参数</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>y</t>
         </is>
       </c>
@@ -499,35 +504,38 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>5.062413525269021</v>
       </c>
       <c r="I2" t="n">
-        <v>3.13</v>
+        <v>3.791987728497095</v>
       </c>
       <c r="J2" t="n">
-        <v>0.96</v>
+        <v>0.005951853773625407</v>
       </c>
       <c r="K2" t="n">
-        <v>48.8</v>
+        <v>32.2317284476686</v>
       </c>
       <c r="L2" t="n">
-        <v>1.89</v>
+        <v>1.140681270509671</v>
       </c>
       <c r="M2" t="n">
-        <v>26.7</v>
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>25.7635909459</v>
       </c>
     </row>
     <row r="3">
@@ -546,35 +554,38 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12.9</v>
+        <v>2.665749044031862</v>
       </c>
       <c r="I3" t="n">
-        <v>2.81</v>
+        <v>4.271687718036644</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07470339817733414</v>
       </c>
       <c r="K3" t="n">
-        <v>41.3</v>
+        <v>45.64140293464357</v>
       </c>
       <c r="L3" t="n">
-        <v>1.96</v>
+        <v>1.223746120233256</v>
       </c>
       <c r="M3" t="n">
-        <v>130</v>
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.4186840738</v>
       </c>
     </row>
     <row r="4">
@@ -593,35 +604,38 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>18.85278117151799</v>
       </c>
       <c r="I4" t="n">
-        <v>2.06</v>
+        <v>3.167495508921816</v>
       </c>
       <c r="J4" t="n">
-        <v>0.63</v>
+        <v>0.4517529276071501</v>
       </c>
       <c r="K4" t="n">
-        <v>37.4</v>
+        <v>31.56710352817567</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.162271754941545</v>
       </c>
       <c r="M4" t="n">
-        <v>227</v>
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>37.7238108537</v>
       </c>
     </row>
     <row r="5">
@@ -640,35 +654,38 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>12.57761364299215</v>
       </c>
       <c r="I5" t="n">
-        <v>3.97</v>
+        <v>3.276937947630793</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1</v>
+        <v>0.59627159988214</v>
       </c>
       <c r="K5" t="n">
-        <v>45.6</v>
+        <v>30.67477180622126</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.057327659836185</v>
       </c>
       <c r="M5" t="n">
-        <v>7.59</v>
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>35.950891708</v>
       </c>
     </row>
     <row r="6">
@@ -687,35 +704,38 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10.7</v>
+        <v>13.24991009209926</v>
       </c>
       <c r="I6" t="n">
-        <v>4.17</v>
+        <v>3.844358149643066</v>
       </c>
       <c r="J6" t="n">
-        <v>0.13</v>
+        <v>0.9924001308317391</v>
       </c>
       <c r="K6" t="n">
-        <v>33.9</v>
+        <v>47.01330368829393</v>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>1.186924807071031</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.7552819228</v>
       </c>
     </row>
     <row r="7">
@@ -734,35 +754,38 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18.7</v>
+        <v>8.790673447594322</v>
       </c>
       <c r="I7" t="n">
-        <v>4.81</v>
+        <v>4.609918071234144</v>
       </c>
       <c r="J7" t="n">
-        <v>0.86</v>
+        <v>0.7601028658090365</v>
       </c>
       <c r="K7" t="n">
-        <v>36.7</v>
+        <v>40.24900794353</v>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.873995785351528</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.1334301655</v>
       </c>
     </row>
     <row r="8">
@@ -781,35 +804,38 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17.9</v>
+        <v>10.09963179088308</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>3.593847236408434</v>
       </c>
       <c r="J8" t="n">
-        <v>0.65</v>
+        <v>0.9573438157193283</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>31.85149412047742</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.854362138116265</v>
       </c>
       <c r="M8" t="n">
-        <v>4.59</v>
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>31.0138425099</v>
       </c>
     </row>
     <row r="9">
@@ -828,35 +854,38 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>13.49310158100068</v>
       </c>
       <c r="I9" t="n">
-        <v>2.39</v>
+        <v>2.906913162239185</v>
       </c>
       <c r="J9" t="n">
-        <v>0.83</v>
+        <v>0.3653126023212286</v>
       </c>
       <c r="K9" t="n">
-        <v>45.5</v>
+        <v>37.10382415783432</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.977475106515995</v>
       </c>
       <c r="M9" t="n">
-        <v>146</v>
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>98.2215639664</v>
       </c>
     </row>
     <row r="10">
@@ -875,35 +904,38 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0.7013100490141464</v>
       </c>
       <c r="I10" t="n">
-        <v>4.69</v>
+        <v>3.935263537164941</v>
       </c>
       <c r="J10" t="n">
-        <v>0.67</v>
+        <v>0.4710443151083625</v>
       </c>
       <c r="K10" t="n">
-        <v>32.9</v>
+        <v>34.1159834447908</v>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>1.382598115251576</v>
       </c>
       <c r="M10" t="n">
-        <v>5.65</v>
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>19.9234843345</v>
       </c>
     </row>
     <row r="11">
@@ -922,35 +954,38 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.1</v>
+        <v>17.47397873451465</v>
       </c>
       <c r="I11" t="n">
-        <v>4.97</v>
+        <v>4.776207085838509</v>
       </c>
       <c r="J11" t="n">
-        <v>0.14</v>
+        <v>0.1615148916379876</v>
       </c>
       <c r="K11" t="n">
-        <v>44.2</v>
+        <v>41.644307013335</v>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>1.680701614599274</v>
       </c>
       <c r="M11" t="n">
-        <v>0.64</v>
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.0970924571</v>
       </c>
     </row>
     <row r="12">
@@ -969,35 +1004,38 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>9.345657632438385</v>
       </c>
       <c r="I12" t="n">
-        <v>3.99</v>
+        <v>2.601523041843269</v>
       </c>
       <c r="J12" t="n">
-        <v>0.82</v>
+        <v>0.9178357673246579</v>
       </c>
       <c r="K12" t="n">
-        <v>40.6</v>
+        <v>46.59253311626606</v>
       </c>
       <c r="L12" t="n">
-        <v>1.98</v>
+        <v>1.072235253466021</v>
       </c>
       <c r="M12" t="n">
-        <v>7.19</v>
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>60.8606407884</v>
       </c>
     </row>
     <row r="13">
@@ -1016,35 +1054,38 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>19.10164407111069</v>
       </c>
       <c r="I13" t="n">
-        <v>2.96</v>
+        <v>3.405823714913251</v>
       </c>
       <c r="J13" t="n">
-        <v>0.24</v>
+        <v>0.02302451499411687</v>
       </c>
       <c r="K13" t="n">
-        <v>42.6</v>
+        <v>41.29037941443531</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.106710126893035</v>
       </c>
       <c r="M13" t="n">
-        <v>6.25</v>
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.12984596</v>
       </c>
     </row>
     <row r="14">
@@ -1063,35 +1104,38 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>17.3</v>
+        <v>18.0095273751258</v>
       </c>
       <c r="I14" t="n">
-        <v>4.63</v>
+        <v>2.957573844255098</v>
       </c>
       <c r="J14" t="n">
-        <v>0.91</v>
+        <v>0.7016475013870674</v>
       </c>
       <c r="K14" t="n">
-        <v>43.3</v>
+        <v>35.82099320347739</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>1.690191344390291</v>
       </c>
       <c r="M14" t="n">
-        <v>0.27</v>
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>51.7825477394</v>
       </c>
     </row>
     <row r="15">
@@ -1110,35 +1154,38 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11.2</v>
+        <v>9.645780985931356</v>
       </c>
       <c r="I15" t="n">
-        <v>3.71</v>
+        <v>3.650014320022908</v>
       </c>
       <c r="J15" t="n">
-        <v>0.32</v>
+        <v>0.1206122404804879</v>
       </c>
       <c r="K15" t="n">
-        <v>33.5</v>
+        <v>45.30427337670349</v>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>1.436054011239916</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15.3756467289</v>
       </c>
     </row>
     <row r="16">
@@ -1157,35 +1204,38 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>17.95253386339844</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>3.288137315905233</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.4348887234775773</v>
       </c>
       <c r="K16" t="n">
-        <v>35.8</v>
+        <v>45.88757709298367</v>
       </c>
       <c r="L16" t="n">
-        <v>1.69</v>
+        <v>1.734416845942168</v>
       </c>
       <c r="M16" t="n">
-        <v>24.6</v>
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>23.6423680486</v>
       </c>
     </row>
     <row r="17">
@@ -1204,35 +1254,38 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15.6</v>
+        <v>11.89294756842407</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>3.737592830262749</v>
       </c>
       <c r="J17" t="n">
-        <v>0.23</v>
+        <v>0.7424857437589109</v>
       </c>
       <c r="K17" t="n">
-        <v>47.4</v>
+        <v>30.93043975144314</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.823981931627264</v>
       </c>
       <c r="M17" t="n">
-        <v>77.59999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>25.3608800509</v>
       </c>
     </row>
     <row r="18">
@@ -1251,35 +1304,38 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7.5</v>
+        <v>1.900899825580328</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>2.258029682265323</v>
       </c>
       <c r="J18" t="n">
-        <v>0.44</v>
+        <v>0.6464730350802288</v>
       </c>
       <c r="K18" t="n">
-        <v>31.5</v>
+        <v>48.78944902281176</v>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>1.286492842150686</v>
       </c>
       <c r="M18" t="n">
-        <v>73.3</v>
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>138.330806048</v>
       </c>
     </row>
     <row r="19">
@@ -1298,35 +1354,38 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.800000000000001</v>
+        <v>5.204033080609687</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>3.008346400650422</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>0.2002117711088549</v>
       </c>
       <c r="K19" t="n">
-        <v>44.6</v>
+        <v>44.90297274047084</v>
       </c>
       <c r="L19" t="n">
-        <v>1.81</v>
+        <v>1.45074529543516</v>
       </c>
       <c r="M19" t="n">
-        <v>25.9</v>
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>48.4008872008</v>
       </c>
     </row>
     <row r="20">
@@ -1345,35 +1404,38 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>3.840222477167763</v>
       </c>
       <c r="I20" t="n">
-        <v>2.26</v>
+        <v>4.394920340976561</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>0.4880431896926373</v>
       </c>
       <c r="K20" t="n">
-        <v>49.5</v>
+        <v>47.84526860803706</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.269719985544889</v>
       </c>
       <c r="M20" t="n">
-        <v>159</v>
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.3670508582</v>
       </c>
     </row>
     <row r="21">
@@ -1392,35 +1454,38 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>7.642483393592121</v>
       </c>
       <c r="I21" t="n">
-        <v>4.13</v>
+        <v>2.256428425100066</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.718958999833033</v>
       </c>
       <c r="K21" t="n">
-        <v>36.1</v>
+        <v>44.78941621760909</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.794464293354486</v>
       </c>
       <c r="M21" t="n">
-        <v>11.8</v>
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>235.764356042</v>
       </c>
     </row>
     <row r="22">
@@ -1439,35 +1504,38 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>11.9</v>
+        <v>0.06992204447974538</v>
       </c>
       <c r="I22" t="n">
-        <v>3.55</v>
+        <v>2.869990185236251</v>
       </c>
       <c r="J22" t="n">
-        <v>0.84</v>
+        <v>0.7520904228777491</v>
       </c>
       <c r="K22" t="n">
-        <v>42</v>
+        <v>32.5451167929636</v>
       </c>
       <c r="L22" t="n">
-        <v>1.74</v>
+        <v>1.743108278366987</v>
       </c>
       <c r="M22" t="n">
-        <v>17.3</v>
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>114.8311281451</v>
       </c>
     </row>
     <row r="23">
@@ -1486,35 +1554,38 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.6</v>
+        <v>1.591854630166177</v>
       </c>
       <c r="I23" t="n">
-        <v>3.58</v>
+        <v>4.62397347636755</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.4052255819331868</v>
       </c>
       <c r="K23" t="n">
-        <v>37.9</v>
+        <v>36.6555481888681</v>
       </c>
       <c r="L23" t="n">
-        <v>1.06</v>
+        <v>1.214153374106737</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.1627749019</v>
       </c>
     </row>
     <row r="24">
@@ -1533,35 +1604,38 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.9</v>
+        <v>19.33591789242409</v>
       </c>
       <c r="I24" t="n">
-        <v>2.01</v>
+        <v>2.384393316863795</v>
       </c>
       <c r="J24" t="n">
-        <v>0.76</v>
+        <v>0.1510763576064068</v>
       </c>
       <c r="K24" t="n">
-        <v>47.8</v>
+        <v>30.18409315946469</v>
       </c>
       <c r="L24" t="n">
-        <v>1.74</v>
+        <v>1.784343250313978</v>
       </c>
       <c r="M24" t="n">
-        <v>306</v>
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>233.8109754146</v>
       </c>
     </row>
     <row r="25">
@@ -1580,35 +1654,38 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.4</v>
+        <v>9.855923236814441</v>
       </c>
       <c r="I25" t="n">
-        <v>2.35</v>
+        <v>4.945558171153561</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1</v>
+        <v>0.1739675930114124</v>
       </c>
       <c r="K25" t="n">
-        <v>39.8</v>
+        <v>49.94310225991894</v>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>1.489856379431405</v>
       </c>
       <c r="M25" t="n">
-        <v>139</v>
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2177983365</v>
       </c>
     </row>
     <row r="26">
@@ -1627,35 +1704,38 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8.699999999999999</v>
+        <v>2.460110919874097</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>3.702653120781987</v>
       </c>
       <c r="J26" t="n">
-        <v>0.54</v>
+        <v>0.825385260929162</v>
       </c>
       <c r="K26" t="n">
-        <v>40.2</v>
+        <v>33.73063995598449</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03</v>
+        <v>1.284777624991522</v>
       </c>
       <c r="M26" t="n">
-        <v>147</v>
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>25.9393363369</v>
       </c>
     </row>
     <row r="27">
@@ -1674,35 +1754,38 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.9</v>
+        <v>7.045072148862791</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>2.517381024584488</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02</v>
+        <v>0.4758209657376068</v>
       </c>
       <c r="K27" t="n">
-        <v>38.4</v>
+        <v>38.78691360399406</v>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>1.048286246661376</v>
       </c>
       <c r="M27" t="n">
-        <v>262</v>
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>99.6506221053</v>
       </c>
     </row>
     <row r="28">
@@ -1721,35 +1804,38 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>14.2</v>
+        <v>4.056434625722959</v>
       </c>
       <c r="I28" t="n">
-        <v>2.91</v>
+        <v>4.030292900864373</v>
       </c>
       <c r="J28" t="n">
-        <v>0.28</v>
+        <v>0.8721998901432417</v>
       </c>
       <c r="K28" t="n">
-        <v>38.6</v>
+        <v>46.05062785719805</v>
       </c>
       <c r="L28" t="n">
-        <v>1.86</v>
+        <v>1.337216176467956</v>
       </c>
       <c r="M28" t="n">
-        <v>87.5</v>
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5.8999629714</v>
       </c>
     </row>
     <row r="29">
@@ -1768,35 +1854,38 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>16.6</v>
+        <v>7.173651487474139</v>
       </c>
       <c r="I29" t="n">
-        <v>2.71</v>
+        <v>2.665862175422327</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.6983601603414773</v>
       </c>
       <c r="K29" t="n">
-        <v>40.9</v>
+        <v>34.7880537519239</v>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.609093205169825</v>
       </c>
       <c r="M29" t="n">
-        <v>50.5</v>
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>132.344419582</v>
       </c>
     </row>
     <row r="30">
@@ -1815,35 +1904,38 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17.2</v>
+        <v>3.342779443388582</v>
       </c>
       <c r="I30" t="n">
-        <v>3.32</v>
+        <v>4.131527757942492</v>
       </c>
       <c r="J30" t="n">
-        <v>0.44</v>
+        <v>0.524257026419388</v>
       </c>
       <c r="K30" t="n">
-        <v>30.8</v>
+        <v>43.81441941405497</v>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>1.867684028052542</v>
       </c>
       <c r="M30" t="n">
-        <v>33.6</v>
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9.2670366353</v>
       </c>
     </row>
     <row r="31">
@@ -1862,35 +1954,38 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>13.74356260724228</v>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>4.192274675013111</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.7886857775784447</v>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>49.65211341218722</v>
       </c>
       <c r="L31" t="n">
-        <v>1.54</v>
+        <v>1.028419783496818</v>
       </c>
       <c r="M31" t="n">
-        <v>9.25</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.64774994</v>
       </c>
     </row>
     <row r="32">
@@ -1909,35 +2004,38 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>12.5</v>
+        <v>11.59562818358859</v>
       </c>
       <c r="I32" t="n">
-        <v>4.35</v>
+        <v>2.332779244336936</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3</v>
+        <v>0.6409191616502946</v>
       </c>
       <c r="K32" t="n">
-        <v>44.9</v>
+        <v>33.24115209489564</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>1.641468352828514</v>
       </c>
       <c r="M32" t="n">
-        <v>2.6</v>
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>190.0443251773</v>
       </c>
     </row>
     <row r="33">
@@ -1956,35 +2054,38 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.8</v>
+        <v>14.44982806319916</v>
       </c>
       <c r="I33" t="n">
-        <v>3.65</v>
+        <v>2.766154930792692</v>
       </c>
       <c r="J33" t="n">
-        <v>0.62</v>
+        <v>0.3937320729575987</v>
       </c>
       <c r="K33" t="n">
-        <v>35.2</v>
+        <v>32.65724818462604</v>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>1.564458395365115</v>
       </c>
       <c r="M33" t="n">
-        <v>25.5</v>
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>96.7718445301</v>
       </c>
     </row>
     <row r="34">
@@ -2003,35 +2104,38 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3.9</v>
+        <v>5.955469141293306</v>
       </c>
       <c r="I34" t="n">
-        <v>3.07</v>
+        <v>3.207545719039907</v>
       </c>
       <c r="J34" t="n">
-        <v>0.38</v>
+        <v>0.6697778156818783</v>
       </c>
       <c r="K34" t="n">
-        <v>42.3</v>
+        <v>48.02328085479147</v>
       </c>
       <c r="L34" t="n">
-        <v>1.97</v>
+        <v>1.000820041092756</v>
       </c>
       <c r="M34" t="n">
-        <v>79.2</v>
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>20.6890330552</v>
       </c>
     </row>
     <row r="35">
@@ -2050,35 +2154,38 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.1</v>
+        <v>10.8913001973412</v>
       </c>
       <c r="I35" t="n">
-        <v>3.26</v>
+        <v>4.844053818655281</v>
       </c>
       <c r="J35" t="n">
-        <v>0.46</v>
+        <v>0.8983249843590705</v>
       </c>
       <c r="K35" t="n">
-        <v>35.5</v>
+        <v>47.40724025620689</v>
       </c>
       <c r="L35" t="n">
-        <v>1.83</v>
+        <v>1.533555775745421</v>
       </c>
       <c r="M35" t="n">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.2119289243</v>
       </c>
     </row>
     <row r="36">
@@ -2097,35 +2204,38 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6.3</v>
+        <v>8.966852074496211</v>
       </c>
       <c r="I36" t="n">
-        <v>4.74</v>
+        <v>4.806456574097062</v>
       </c>
       <c r="J36" t="n">
-        <v>0.19</v>
+        <v>0.1080665748294484</v>
       </c>
       <c r="K36" t="n">
-        <v>39</v>
+        <v>41.12783897288482</v>
       </c>
       <c r="L36" t="n">
-        <v>1.77</v>
+        <v>1.398569606760724</v>
       </c>
       <c r="M36" t="n">
-        <v>1.03</v>
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.1139757075</v>
       </c>
     </row>
     <row r="37">
@@ -2144,35 +2254,38 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>13.9</v>
+        <v>11.26631799477363</v>
       </c>
       <c r="I37" t="n">
-        <v>4.05</v>
+        <v>4.501071446155674</v>
       </c>
       <c r="J37" t="n">
-        <v>0.06</v>
+        <v>0.9310392396521507</v>
       </c>
       <c r="K37" t="n">
-        <v>30.7</v>
+        <v>38.02748652958869</v>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>1.402131118624471</v>
       </c>
       <c r="M37" t="n">
-        <v>1.12</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.0192141075</v>
       </c>
     </row>
     <row r="38">
@@ -2191,35 +2304,38 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>16.3</v>
+        <v>1.102293525131624</v>
       </c>
       <c r="I38" t="n">
-        <v>4.32</v>
+        <v>4.183739027358044</v>
       </c>
       <c r="J38" t="n">
-        <v>0.37</v>
+        <v>0.9491751536059778</v>
       </c>
       <c r="K38" t="n">
-        <v>34.3</v>
+        <v>41.78005564747879</v>
       </c>
       <c r="L38" t="n">
-        <v>1.11</v>
+        <v>1.543884795757566</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>8.0490064502</v>
       </c>
     </row>
     <row r="39">
@@ -2238,35 +2354,38 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3.5</v>
+        <v>15.66277796247286</v>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>2.849165883452228</v>
       </c>
       <c r="J39" t="n">
-        <v>0.21</v>
+        <v>0.5587750501609965</v>
       </c>
       <c r="K39" t="n">
-        <v>37.2</v>
+        <v>38.88874559911995</v>
       </c>
       <c r="L39" t="n">
-        <v>1.65</v>
+        <v>1.65712726113723</v>
       </c>
       <c r="M39" t="n">
-        <v>2.72</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>63.402148311</v>
       </c>
     </row>
     <row r="40">
@@ -2285,35 +2404,38 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.7</v>
+        <v>2.011829171013445</v>
       </c>
       <c r="I40" t="n">
-        <v>4.85</v>
+        <v>4.982946433255744</v>
       </c>
       <c r="J40" t="n">
-        <v>0.34</v>
+        <v>0.7752086373792334</v>
       </c>
       <c r="K40" t="n">
-        <v>42.9</v>
+        <v>40.44414262722661</v>
       </c>
       <c r="L40" t="n">
-        <v>1.43</v>
+        <v>1.526928039229538</v>
       </c>
       <c r="M40" t="n">
-        <v>0.793</v>
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.7676019166</v>
       </c>
     </row>
     <row r="41">
@@ -2332,35 +2454,38 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.4</v>
+        <v>8.057353332275071</v>
       </c>
       <c r="I41" t="n">
-        <v>2.74</v>
+        <v>2.719337566404529</v>
       </c>
       <c r="J41" t="n">
-        <v>0.92</v>
+        <v>0.2905839226204517</v>
       </c>
       <c r="K41" t="n">
-        <v>46.3</v>
+        <v>43.27720345897131</v>
       </c>
       <c r="L41" t="n">
-        <v>1.1</v>
+        <v>1.813000024386284</v>
       </c>
       <c r="M41" t="n">
-        <v>29.5</v>
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>117.360931543</v>
       </c>
     </row>
     <row r="42">
@@ -2379,35 +2504,38 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9.9</v>
+        <v>19.90458937001179</v>
       </c>
       <c r="I42" t="n">
-        <v>2.61</v>
+        <v>2.047725514144118</v>
       </c>
       <c r="J42" t="n">
-        <v>0.52</v>
+        <v>0.8495371409978675</v>
       </c>
       <c r="K42" t="n">
-        <v>32.8</v>
+        <v>33.02518878030984</v>
       </c>
       <c r="L42" t="n">
-        <v>1.18</v>
+        <v>1.508364709487392</v>
       </c>
       <c r="M42" t="n">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>202.6956687735</v>
       </c>
     </row>
     <row r="43">
@@ -2426,35 +2554,38 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>9.300000000000001</v>
+        <v>16.46418142145759</v>
       </c>
       <c r="I43" t="n">
-        <v>4.54</v>
+        <v>3.081001101539367</v>
       </c>
       <c r="J43" t="n">
-        <v>0.28</v>
+        <v>0.09255328064414502</v>
       </c>
       <c r="K43" t="n">
-        <v>30</v>
+        <v>42.60396112902578</v>
       </c>
       <c r="L43" t="n">
-        <v>1.79</v>
+        <v>1.326029602044023</v>
       </c>
       <c r="M43" t="n">
-        <v>1.05</v>
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>41.6378573914</v>
       </c>
     </row>
     <row r="44">
@@ -2473,35 +2604,38 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7.7</v>
+        <v>17.19647104757645</v>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>3.816602089132247</v>
       </c>
       <c r="J44" t="n">
-        <v>0.77</v>
+        <v>0.6842032510072414</v>
       </c>
       <c r="K44" t="n">
-        <v>49.7</v>
+        <v>48.55583670630409</v>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>1.766551629690004</v>
       </c>
       <c r="M44" t="n">
-        <v>20.1</v>
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.8557890783</v>
       </c>
     </row>
     <row r="45">
@@ -2520,35 +2654,38 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>19.7</v>
+        <v>3.667384353471965</v>
       </c>
       <c r="I45" t="n">
-        <v>2.59</v>
+        <v>3.455920907510218</v>
       </c>
       <c r="J45" t="n">
-        <v>0.97</v>
+        <v>0.3096076938818357</v>
       </c>
       <c r="K45" t="n">
-        <v>39.5</v>
+        <v>40.66094696734164</v>
       </c>
       <c r="L45" t="n">
-        <v>1.42</v>
+        <v>1.952383498083852</v>
       </c>
       <c r="M45" t="n">
-        <v>59.8</v>
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>41.4504238196</v>
       </c>
     </row>
     <row r="46">
@@ -2567,35 +2704,38 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4.8</v>
+        <v>2.955997692845935</v>
       </c>
       <c r="I46" t="n">
-        <v>2.47</v>
+        <v>4.87891048766206</v>
       </c>
       <c r="J46" t="n">
-        <v>0.16</v>
+        <v>0.381462135227806</v>
       </c>
       <c r="K46" t="n">
-        <v>43.9</v>
+        <v>37.34586475668765</v>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.144171484741881</v>
       </c>
       <c r="M46" t="n">
-        <v>149</v>
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.5090419126</v>
       </c>
     </row>
     <row r="47">
@@ -2614,35 +2754,38 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.1</v>
+        <v>14.84103237129497</v>
       </c>
       <c r="I47" t="n">
-        <v>3.36</v>
+        <v>2.014349627992551</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6</v>
+        <v>0.8020226694473304</v>
       </c>
       <c r="K47" t="n">
-        <v>49</v>
+        <v>42.99768559564909</v>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.839395368602891</v>
       </c>
       <c r="M47" t="n">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>284.6091582199</v>
       </c>
     </row>
     <row r="48">
@@ -2661,35 +2804,38 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5.9</v>
+        <v>4.660867155827573</v>
       </c>
       <c r="I48" t="n">
-        <v>3.87</v>
+        <v>4.323024953433192</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.545470566982597</v>
       </c>
       <c r="K48" t="n">
-        <v>32.4</v>
+        <v>35.25434498854942</v>
       </c>
       <c r="L48" t="n">
-        <v>1.29</v>
+        <v>1.231256047380415</v>
       </c>
       <c r="M48" t="n">
-        <v>21.5</v>
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>8.353070521099999</v>
       </c>
     </row>
     <row r="49">
@@ -2708,35 +2854,38 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.2</v>
+        <v>1.421849104062233</v>
       </c>
       <c r="I49" t="n">
-        <v>4.45</v>
+        <v>4.680977997952107</v>
       </c>
       <c r="J49" t="n">
-        <v>0.71</v>
+        <v>0.8675091406244609</v>
       </c>
       <c r="K49" t="n">
-        <v>48.3</v>
+        <v>35.6997167554447</v>
       </c>
       <c r="L49" t="n">
-        <v>1.26</v>
+        <v>1.308721994202662</v>
       </c>
       <c r="M49" t="n">
-        <v>1.07</v>
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4.3918628197</v>
       </c>
     </row>
     <row r="50">
@@ -2755,35 +2904,38 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>14.7</v>
+        <v>8.454657159618288</v>
       </c>
       <c r="I50" t="n">
-        <v>4.26</v>
+        <v>3.545650335219139</v>
       </c>
       <c r="J50" t="n">
-        <v>0.73</v>
+        <v>0.504267099674667</v>
       </c>
       <c r="K50" t="n">
-        <v>46.5</v>
+        <v>39.80892250192775</v>
       </c>
       <c r="L50" t="n">
-        <v>1.06</v>
+        <v>1.889615782416802</v>
       </c>
       <c r="M50" t="n">
-        <v>0.777</v>
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>30.7782870899</v>
       </c>
     </row>
     <row r="51">
@@ -2802,35 +2954,38 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12.3</v>
+        <v>12.1351579719514</v>
       </c>
       <c r="I51" t="n">
-        <v>2.87</v>
+        <v>4.571273352761962</v>
       </c>
       <c r="J51" t="n">
-        <v>0.41</v>
+        <v>0.2515027426485515</v>
       </c>
       <c r="K51" t="n">
-        <v>34.5</v>
+        <v>31.21443128022999</v>
       </c>
       <c r="L51" t="n">
-        <v>1.63</v>
+        <v>1.585253826727029</v>
       </c>
       <c r="M51" t="n">
-        <v>84.3</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.0552177592</v>
       </c>
     </row>
     <row r="52">
@@ -2849,35 +3004,38 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.4</v>
+        <v>15.31336204051337</v>
       </c>
       <c r="I52" t="n">
-        <v>4.31</v>
+        <v>3.470805661866575</v>
       </c>
       <c r="J52" t="n">
-        <v>0.73</v>
+        <v>0.6170205520091783</v>
       </c>
       <c r="K52" t="n">
-        <v>44.6</v>
+        <v>48.91103558284612</v>
       </c>
       <c r="L52" t="n">
-        <v>1.16</v>
+        <v>1.460259886739246</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>11.0869968009</v>
       </c>
     </row>
     <row r="53">
@@ -2896,35 +3054,38 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.3</v>
+        <v>19.64480613135922</v>
       </c>
       <c r="I53" t="n">
-        <v>2.26</v>
+        <v>4.254386118548692</v>
       </c>
       <c r="J53" t="n">
-        <v>0.63</v>
+        <v>0.06873688586012641</v>
       </c>
       <c r="K53" t="n">
-        <v>47.4</v>
+        <v>34.55813149827203</v>
       </c>
       <c r="L53" t="n">
-        <v>1.1</v>
+        <v>1.473737301755897</v>
       </c>
       <c r="M53" t="n">
-        <v>118</v>
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.0539344156</v>
       </c>
     </row>
     <row r="54">
@@ -2943,35 +3104,38 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13.4</v>
+        <v>6.536435116647663</v>
       </c>
       <c r="I54" t="n">
-        <v>4.41</v>
+        <v>2.774520121157507</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6075782920081106</v>
       </c>
       <c r="K54" t="n">
-        <v>34.9</v>
+        <v>44.40922652805584</v>
       </c>
       <c r="L54" t="n">
-        <v>1.76</v>
+        <v>1.915584523438366</v>
       </c>
       <c r="M54" t="n">
-        <v>4.56</v>
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>112.1733243692</v>
       </c>
     </row>
     <row r="55">
@@ -2990,35 +3154,38 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>19.5</v>
+        <v>6.597607864050948</v>
       </c>
       <c r="I55" t="n">
-        <v>3.91</v>
+        <v>3.061144880499682</v>
       </c>
       <c r="J55" t="n">
-        <v>0.26</v>
+        <v>0.5408093734145148</v>
       </c>
       <c r="K55" t="n">
-        <v>49.4</v>
+        <v>46.4471784781482</v>
       </c>
       <c r="L55" t="n">
-        <v>1.87</v>
+        <v>1.705506857308574</v>
       </c>
       <c r="M55" t="n">
-        <v>1.06</v>
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>48.6361321868</v>
       </c>
     </row>
     <row r="56">
@@ -3037,35 +3204,38 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>4.1</v>
+        <v>5.626179887147902</v>
       </c>
       <c r="I56" t="n">
-        <v>2.54</v>
+        <v>2.207173349442134</v>
       </c>
       <c r="J56" t="n">
-        <v>0.85</v>
+        <v>0.901938153571176</v>
       </c>
       <c r="K56" t="n">
-        <v>31.8</v>
+        <v>37.93573261155042</v>
       </c>
       <c r="L56" t="n">
-        <v>1.51</v>
+        <v>1.087868904791909</v>
       </c>
       <c r="M56" t="n">
-        <v>166</v>
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>170.1163161718</v>
       </c>
     </row>
     <row r="57">
@@ -3084,35 +3254,38 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>6.7</v>
+        <v>12.55444681955272</v>
       </c>
       <c r="I57" t="n">
-        <v>2.96</v>
+        <v>2.494710393837861</v>
       </c>
       <c r="J57" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2655844393114011</v>
       </c>
       <c r="K57" t="n">
-        <v>41.3</v>
+        <v>42.42515053183661</v>
       </c>
       <c r="L57" t="n">
-        <v>1.28</v>
+        <v>1.614868491768987</v>
       </c>
       <c r="M57" t="n">
-        <v>56.2</v>
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>128.9813615363</v>
       </c>
     </row>
     <row r="58">
@@ -3131,35 +3304,38 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>16</v>
+        <v>15.82747266044442</v>
       </c>
       <c r="I58" t="n">
-        <v>3.67</v>
+        <v>4.061427701866835</v>
       </c>
       <c r="J58" t="n">
-        <v>0.35</v>
+        <v>0.1980493907085382</v>
       </c>
       <c r="K58" t="n">
-        <v>37</v>
+        <v>44.00554791682609</v>
       </c>
       <c r="L58" t="n">
-        <v>1.44</v>
+        <v>1.347991778152457</v>
       </c>
       <c r="M58" t="n">
-        <v>18.3</v>
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.0459808155</v>
       </c>
     </row>
     <row r="59">
@@ -3178,35 +3354,38 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>10.4</v>
+        <v>16.74121259536058</v>
       </c>
       <c r="I59" t="n">
-        <v>4.84</v>
+        <v>4.742820523002895</v>
       </c>
       <c r="J59" t="n">
-        <v>0.54</v>
+        <v>0.04963987031550014</v>
       </c>
       <c r="K59" t="n">
-        <v>43.6</v>
+        <v>47.64256371147479</v>
       </c>
       <c r="L59" t="n">
-        <v>1.36</v>
+        <v>1.593200925608215</v>
       </c>
       <c r="M59" t="n">
-        <v>0.391</v>
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.5708672232000001</v>
       </c>
     </row>
     <row r="60">
@@ -3225,35 +3404,38 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.6</v>
+        <v>14.15321135096067</v>
       </c>
       <c r="I60" t="n">
-        <v>2.67</v>
+        <v>2.469897833371066</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1</v>
+        <v>0.8315751641316175</v>
       </c>
       <c r="K60" t="n">
-        <v>39.1</v>
+        <v>36.03000272954156</v>
       </c>
       <c r="L60" t="n">
-        <v>1.97</v>
+        <v>1.37039161567866</v>
       </c>
       <c r="M60" t="n">
-        <v>179</v>
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>101.8133348736</v>
       </c>
     </row>
     <row r="61">
@@ -3272,35 +3454,38 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14.5</v>
+        <v>10.84856623608442</v>
       </c>
       <c r="I61" t="n">
-        <v>3.42</v>
+        <v>3.118583246009112</v>
       </c>
       <c r="J61" t="n">
-        <v>0.45</v>
+        <v>0.5806925900887516</v>
       </c>
       <c r="K61" t="n">
-        <v>32</v>
+        <v>38.36693601750534</v>
       </c>
       <c r="L61" t="n">
-        <v>1.64</v>
+        <v>1.998681066699485</v>
       </c>
       <c r="M61" t="n">
-        <v>37.3</v>
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>63.8482931639</v>
       </c>
     </row>
     <row r="62">
@@ -3319,35 +3504,38 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>17.14208018787137</v>
       </c>
       <c r="I62" t="n">
-        <v>3.63</v>
+        <v>2.589404107986309</v>
       </c>
       <c r="J62" t="n">
-        <v>0.06</v>
+        <v>0.2197492572535154</v>
       </c>
       <c r="K62" t="n">
-        <v>42.2</v>
+        <v>30.42297470046075</v>
       </c>
       <c r="L62" t="n">
-        <v>1.02</v>
+        <v>1.906208663406243</v>
       </c>
       <c r="M62" t="n">
-        <v>16.1</v>
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>190.3071713879</v>
       </c>
     </row>
     <row r="63">
@@ -3366,35 +3554,38 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>14.4</v>
+        <v>16.27429404694184</v>
       </c>
       <c r="I63" t="n">
-        <v>2.93</v>
+        <v>2.119107614506995</v>
       </c>
       <c r="J63" t="n">
-        <v>0.29</v>
+        <v>0.2738088660559075</v>
       </c>
       <c r="K63" t="n">
-        <v>31.7</v>
+        <v>39.29251688287694</v>
       </c>
       <c r="L63" t="n">
-        <v>1.73</v>
+        <v>1.12735126227149</v>
       </c>
       <c r="M63" t="n">
-        <v>96.09999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>160.6212943579</v>
       </c>
     </row>
     <row r="64">
@@ -3413,35 +3604,38 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.2</v>
+        <v>6.102280804387526</v>
       </c>
       <c r="I64" t="n">
-        <v>3.65</v>
+        <v>3.342739208180324</v>
       </c>
       <c r="J64" t="n">
-        <v>0.45</v>
+        <v>0.2322323016893712</v>
       </c>
       <c r="K64" t="n">
-        <v>30.1</v>
+        <v>49.20611730665426</v>
       </c>
       <c r="L64" t="n">
-        <v>1.19</v>
+        <v>1.719945915499671</v>
       </c>
       <c r="M64" t="n">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>26.9274119148</v>
       </c>
     </row>
     <row r="65">
@@ -3460,35 +3654,38 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>9.699999999999999</v>
+        <v>0.5532206352181539</v>
       </c>
       <c r="I65" t="n">
-        <v>2.28</v>
+        <v>2.410830632488139</v>
       </c>
       <c r="J65" t="n">
-        <v>0.77</v>
+        <v>0.9745551919485183</v>
       </c>
       <c r="K65" t="n">
-        <v>39.2</v>
+        <v>37.45027141396785</v>
       </c>
       <c r="L65" t="n">
-        <v>1.83</v>
+        <v>1.177762621664662</v>
       </c>
       <c r="M65" t="n">
-        <v>239</v>
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>132.0631902463</v>
       </c>
     </row>
     <row r="66">
@@ -3507,35 +3704,38 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.5</v>
+        <v>7.73999537019418</v>
       </c>
       <c r="I66" t="n">
-        <v>4.45</v>
+        <v>4.402213270916744</v>
       </c>
       <c r="J66" t="n">
-        <v>0.87</v>
+        <v>0.1385120942984543</v>
       </c>
       <c r="K66" t="n">
-        <v>48.8</v>
+        <v>42.01383677543964</v>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>1.667999484797672</v>
       </c>
       <c r="M66" t="n">
-        <v>1.65</v>
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5.0121689721</v>
       </c>
     </row>
     <row r="67">
@@ -3554,35 +3754,38 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>11</v>
+        <v>4.306095240756662</v>
       </c>
       <c r="I67" t="n">
-        <v>4.83</v>
+        <v>3.926277840071466</v>
       </c>
       <c r="J67" t="n">
-        <v>0.13</v>
+        <v>0.3368149277658787</v>
       </c>
       <c r="K67" t="n">
-        <v>32.1</v>
+        <v>43.46333691887615</v>
       </c>
       <c r="L67" t="n">
-        <v>1.54</v>
+        <v>1.42742847549842</v>
       </c>
       <c r="M67" t="n">
-        <v>1.04</v>
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>10.2058147076</v>
       </c>
     </row>
     <row r="68">
@@ -3601,35 +3804,38 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>13.9</v>
+        <v>10.33742646924462</v>
       </c>
       <c r="I68" t="n">
-        <v>4.13</v>
+        <v>2.156129167466597</v>
       </c>
       <c r="J68" t="n">
-        <v>0.53</v>
+        <v>0.3219072870334412</v>
       </c>
       <c r="K68" t="n">
-        <v>40.2</v>
+        <v>36.55110959481253</v>
       </c>
       <c r="L68" t="n">
-        <v>1.9</v>
+        <v>1.037783408961387</v>
       </c>
       <c r="M68" t="n">
-        <v>7.98</v>
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>167.8439754411</v>
       </c>
     </row>
     <row r="69">
@@ -3648,35 +3854,38 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>17.9</v>
+        <v>12.99969541731777</v>
       </c>
       <c r="I69" t="n">
-        <v>3.45</v>
+        <v>4.474376580025294</v>
       </c>
       <c r="J69" t="n">
-        <v>0.68</v>
+        <v>0.4185094969201203</v>
       </c>
       <c r="K69" t="n">
-        <v>38.9</v>
+        <v>33.67358580785395</v>
       </c>
       <c r="L69" t="n">
-        <v>1.79</v>
+        <v>1.249700813350074</v>
       </c>
       <c r="M69" t="n">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1.0569250323</v>
       </c>
     </row>
     <row r="70">
@@ -3695,35 +3904,38 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>7.9</v>
+        <v>14.9630109088512</v>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>3.519626457308718</v>
       </c>
       <c r="J70" t="n">
-        <v>0.22</v>
+        <v>0.03062173650601431</v>
       </c>
       <c r="K70" t="n">
-        <v>33.8</v>
+        <v>39.66167798514045</v>
       </c>
       <c r="L70" t="n">
-        <v>1.25</v>
+        <v>1.939740854571276</v>
       </c>
       <c r="M70" t="n">
-        <v>2.4</v>
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>41.112496892</v>
       </c>
     </row>
     <row r="71">
@@ -3742,35 +3954,38 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>20</v>
+        <v>18.4588692619293</v>
       </c>
       <c r="I71" t="n">
-        <v>3.93</v>
+        <v>4.007182135571664</v>
       </c>
       <c r="J71" t="n">
-        <v>0.38</v>
+        <v>0.3555537985492461</v>
       </c>
       <c r="K71" t="n">
-        <v>36.2</v>
+        <v>35.13541920449595</v>
       </c>
       <c r="L71" t="n">
-        <v>1.45</v>
+        <v>1.957732484086177</v>
       </c>
       <c r="M71" t="n">
-        <v>10.9</v>
+        <v>1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>15.2928715242</v>
       </c>
     </row>
   </sheetData>
